--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q40_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0279859504399631</v>
+        <v>0.01435314511439574</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0279859504399631</v>
+        <v>0.01435314511439574</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02585131731815648</v>
+        <v>0.01311658059375833</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02585131731815648</v>
+        <v>0.01311658059375833</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03119407444149191</v>
+        <v>0.01606807224751243</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03119407444149191</v>
+        <v>0.01606807224751243</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04921226968086555</v>
+        <v>0.02572855942579216</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04921226968086555</v>
+        <v>0.02572855942579216</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07511131519792236</v>
+        <v>0.03930418616488329</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07511131519792236</v>
+        <v>0.03930418616488329</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1023029455468033</v>
+        <v>0.05325997615726743</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1023029455468033</v>
+        <v>0.05325997615726743</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1386128465620165</v>
+        <v>0.07219203129518019</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1386128465620165</v>
+        <v>0.07219203129518019</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1736502983846257</v>
+        <v>0.09067612645985421</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1736502983846257</v>
+        <v>0.09067612645985421</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1986219316988943</v>
+        <v>0.1038154510953368</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1986219316988943</v>
+        <v>0.1038154510953368</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2108965439782625</v>
+        <v>0.110129767245891</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2108965439782625</v>
+        <v>0.110129767245891</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2101349810069583</v>
+        <v>0.1095703569262112</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2101349810069583</v>
+        <v>0.1095703569262112</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2034949155212955</v>
+        <v>0.1060441522369518</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2034949155212955</v>
+        <v>0.1060441522369518</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1946345280954568</v>
+        <v>0.1014771925303859</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1946345280954568</v>
+        <v>0.1014771925303859</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1813687342750915</v>
+        <v>0.09460406099228001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1813687342750915</v>
+        <v>0.09460406099228001</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1781143634900922</v>
+        <v>0.09297694539760591</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1781143634900922</v>
+        <v>0.09297694539760591</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1671261388607233</v>
+        <v>0.08730720366380523</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1671261388607233</v>
+        <v>0.08730720366380523</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1605915798626208</v>
+        <v>0.08396101373122065</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1605915798626208</v>
+        <v>0.08396101373122065</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1652417166479457</v>
+        <v>0.08645219328325482</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1652417166479457</v>
+        <v>0.08645219328325482</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1551901790777044</v>
+        <v>0.08128282232987281</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1551901790777044</v>
+        <v>0.08128282232987281</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1517767118159996</v>
+        <v>0.07953080361500386</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1517767118159996</v>
+        <v>0.07953080361500386</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
